--- a/Financial Analysis/TTWO.xlsx
+++ b/Financial Analysis/TTWO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD286FF6-C7C5-4A30-A0C2-AC5E6F01C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAEED1A-D483-4E6F-8E7D-C37B7D03FCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4E1C87E7-E382-44AE-8697-EE947DCD8AC3}"/>
   </bookViews>
@@ -341,14 +341,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -365,7 +365,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6995160" y="7620"/>
+          <a:off x="10096500" y="7620"/>
           <a:ext cx="0" cy="7597140"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -767,17 +767,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>249.98</v>
+        <v>223.03</v>
       </c>
       <c r="E3" s="4">
-        <v>45909</v>
+        <v>46057</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45909</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="4">
-        <v>45967</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -785,8 +785,8 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>184.5</f>
-        <v>184.5</v>
+        <f>184.6</f>
+        <v>184.6</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>36</v>
@@ -798,7 +798,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>46121.31</v>
+        <v>41171.337999999996</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -806,11 +806,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>1456.1+9.4</f>
-        <v>1465.5</v>
+        <f>2160+199+78.6</f>
+        <v>2437.6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -818,11 +818,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>1148.5+2512.6</f>
-        <v>3661.1</v>
+        <f>582.2+2487</f>
+        <v>3069.2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -831,7 +831,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>-2195.6</v>
+        <v>-631.59999999999991</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -840,7 +840,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>48316.909999999996</v>
+        <v>41802.937999999995</v>
       </c>
     </row>
   </sheetData>
@@ -1075,12 +1075,10 @@
         <v>1382.5</v>
       </c>
       <c r="L3" s="6">
-        <f>H3*1.13</f>
-        <v>1394.307</v>
+        <v>1640.9</v>
       </c>
       <c r="M3" s="6">
-        <f>I3*1.12</f>
-        <v>1392.2719999999999</v>
+        <v>1570.3</v>
       </c>
       <c r="N3" s="6">
         <f>J3*1.02</f>
@@ -1103,7 +1101,7 @@
       </c>
       <c r="X3" s="6">
         <f>SUM(K3:N3)</f>
-        <v>5672.3549999999996</v>
+        <v>6096.9759999999997</v>
       </c>
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
@@ -1147,12 +1145,10 @@
         <v>121.3</v>
       </c>
       <c r="L4" s="6">
-        <f>H4*1.05</f>
-        <v>125.16000000000001</v>
+        <v>132.9</v>
       </c>
       <c r="M4" s="6">
-        <f t="shared" ref="M4" si="0">I4*1.05</f>
-        <v>122.53500000000001</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="N4" s="6">
         <f>J4*1.2</f>
@@ -1175,7 +1171,7 @@
       </c>
       <c r="X4" s="6">
         <f>SUM(K4:N4)</f>
-        <v>499.435</v>
+        <v>513.33999999999992</v>
       </c>
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
@@ -1192,112 +1188,112 @@
         <v>13</v>
       </c>
       <c r="C5" s="9">
-        <f t="shared" ref="C5:K5" si="1">C3+C4</f>
+        <f t="shared" ref="C5:K5" si="0">C3+C4</f>
         <v>1284.6999999999998</v>
       </c>
       <c r="D5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1299.1999999999998</v>
       </c>
       <c r="E5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1366.3</v>
       </c>
       <c r="F5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1399.3999999999999</v>
       </c>
       <c r="G5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1338.2</v>
       </c>
       <c r="H5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1353.1000000000001</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1359.8</v>
       </c>
       <c r="J5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1582.5</v>
       </c>
       <c r="K5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1503.8</v>
       </c>
       <c r="L5" s="9">
-        <f t="shared" ref="L5" si="2">L3+L4</f>
-        <v>1519.4670000000001</v>
+        <f t="shared" ref="L5" si="1">L3+L4</f>
+        <v>1773.8000000000002</v>
       </c>
       <c r="M5" s="9">
-        <f t="shared" ref="M5" si="3">M3+M4</f>
-        <v>1514.807</v>
+        <f t="shared" ref="M5" si="2">M3+M4</f>
+        <v>1699</v>
       </c>
       <c r="N5" s="9">
-        <f t="shared" ref="N5" si="4">N3+N4</f>
+        <f t="shared" ref="N5" si="3">N3+N4</f>
         <v>1633.7160000000001</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" ref="S5:X5" si="5">S3+S4</f>
+        <f t="shared" ref="S5:X5" si="4">S3+S4</f>
         <v>3372.7999999999997</v>
       </c>
       <c r="T5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3504.7999999999997</v>
       </c>
       <c r="U5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5349.9000000000005</v>
       </c>
       <c r="V5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5349.6</v>
       </c>
       <c r="W5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5633.6</v>
       </c>
       <c r="X5" s="9">
-        <f t="shared" si="5"/>
-        <v>6171.79</v>
+        <f t="shared" si="4"/>
+        <v>6610.3159999999998</v>
       </c>
       <c r="Y5" s="9">
-        <f>X5*1.7</f>
-        <v>10492.043</v>
+        <f>X5*1.4</f>
+        <v>9254.4423999999999</v>
       </c>
       <c r="Z5" s="9">
-        <f>Y5*0.93</f>
-        <v>9757.5999900000006</v>
+        <f>Y5*1.15</f>
+        <v>10642.608759999999</v>
       </c>
       <c r="AA5" s="9">
         <f>Z5*1.02</f>
-        <v>9952.751989800001</v>
+        <v>10855.460935199999</v>
       </c>
       <c r="AB5" s="9">
         <f>AA5*1.01</f>
-        <v>10052.279509698001</v>
+        <v>10964.015544551999</v>
       </c>
       <c r="AC5" s="9">
-        <f t="shared" ref="AC5:AG5" si="6">AB5*1.01</f>
-        <v>10152.802304794981</v>
+        <f t="shared" ref="AC5:AG5" si="5">AB5*1.01</f>
+        <v>11073.65569999752</v>
       </c>
       <c r="AD5" s="9">
-        <f t="shared" si="6"/>
-        <v>10254.33032784293</v>
+        <f t="shared" si="5"/>
+        <v>11184.392256997495</v>
       </c>
       <c r="AE5" s="9">
-        <f t="shared" si="6"/>
-        <v>10356.87363112136</v>
+        <f t="shared" si="5"/>
+        <v>11296.23617956747</v>
       </c>
       <c r="AF5" s="9">
-        <f t="shared" si="6"/>
-        <v>10460.442367432574</v>
+        <f t="shared" si="5"/>
+        <v>11409.198541363145</v>
       </c>
       <c r="AG5" s="9">
-        <f t="shared" si="6"/>
-        <v>10565.046791106899</v>
+        <f t="shared" si="5"/>
+        <v>11523.290526776776</v>
       </c>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.3">
@@ -1332,15 +1328,13 @@
         <v>558.79999999999995</v>
       </c>
       <c r="L6" s="6">
-        <f>L5-L7</f>
-        <v>653.37081000000012</v>
+        <v>793.3</v>
       </c>
       <c r="M6" s="6">
-        <f t="shared" ref="M6:N6" si="7">M5-M7</f>
-        <v>651.36701000000005</v>
+        <v>753.5</v>
       </c>
       <c r="N6" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="N6" si="6">N5-N7</f>
         <v>702.49788000000012</v>
       </c>
       <c r="S6" s="6">
@@ -1360,43 +1354,43 @@
       </c>
       <c r="X6" s="6">
         <f>SUM(K6:N6)</f>
-        <v>2566.0357000000004</v>
+        <v>2808.0978800000003</v>
       </c>
       <c r="Y6" s="6">
         <f>Y5-Y7</f>
-        <v>4406.6580600000007</v>
+        <v>3886.8658080000005</v>
       </c>
       <c r="Z6" s="6">
-        <f t="shared" ref="Z6:AG6" si="8">Z5-Z7</f>
-        <v>4098.1919958000008</v>
+        <f t="shared" ref="Z6:AG6" si="7">Z5-Z7</f>
+        <v>4469.8956791999999</v>
       </c>
       <c r="AA6" s="6">
-        <f t="shared" si="8"/>
-        <v>4180.1558357160011</v>
+        <f t="shared" si="7"/>
+        <v>4559.2935927839999</v>
       </c>
       <c r="AB6" s="6">
-        <f t="shared" si="8"/>
-        <v>4221.9573940731607</v>
+        <f t="shared" si="7"/>
+        <v>4604.8865287118406</v>
       </c>
       <c r="AC6" s="6">
-        <f t="shared" si="8"/>
-        <v>4264.1769680138923</v>
+        <f t="shared" si="7"/>
+        <v>4650.9353939989587</v>
       </c>
       <c r="AD6" s="6">
-        <f t="shared" si="8"/>
-        <v>4306.8187376940314</v>
+        <f t="shared" si="7"/>
+        <v>4697.4447479389482</v>
       </c>
       <c r="AE6" s="6">
-        <f t="shared" si="8"/>
-        <v>4349.8869250709713</v>
+        <f t="shared" si="7"/>
+        <v>4744.4191954183379</v>
       </c>
       <c r="AF6" s="6">
-        <f t="shared" si="8"/>
-        <v>4393.3857943216817</v>
+        <f t="shared" si="7"/>
+        <v>4791.8633873725212</v>
       </c>
       <c r="AG6" s="6">
-        <f t="shared" si="8"/>
-        <v>4437.3196522648977</v>
+        <f t="shared" si="7"/>
+        <v>4839.7820212462466</v>
       </c>
     </row>
     <row r="7" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1404,112 +1398,112 @@
         <v>15</v>
       </c>
       <c r="C7" s="9">
-        <f t="shared" ref="C7:K7" si="9">C5-C6</f>
+        <f t="shared" ref="C7:M7" si="8">C5-C6</f>
         <v>679.19999999999982</v>
       </c>
       <c r="D7" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>415.39999999999986</v>
       </c>
       <c r="E7" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>678.09999999999991</v>
       </c>
       <c r="F7" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>469.09999999999991</v>
       </c>
       <c r="G7" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>771.1</v>
       </c>
       <c r="H7" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>727.90000000000009</v>
       </c>
       <c r="I7" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>759.9</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>803.3</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>945</v>
       </c>
       <c r="L7" s="9">
-        <f>L5*0.57</f>
-        <v>866.09618999999998</v>
+        <f t="shared" si="8"/>
+        <v>980.50000000000023</v>
       </c>
       <c r="M7" s="9">
-        <f t="shared" ref="M7:N7" si="10">M5*0.57</f>
-        <v>863.43998999999997</v>
+        <f t="shared" si="8"/>
+        <v>945.5</v>
       </c>
       <c r="N7" s="9">
+        <f t="shared" ref="N7" si="9">N5*0.57</f>
+        <v>931.21812</v>
+      </c>
+      <c r="S7" s="9">
+        <f t="shared" ref="S7:X7" si="10">S5-S6</f>
+        <v>1837.6999999999998</v>
+      </c>
+      <c r="T7" s="9">
         <f t="shared" si="10"/>
-        <v>931.21812</v>
-      </c>
-      <c r="S7" s="9">
-        <f t="shared" ref="S7:X7" si="11">S5-S6</f>
-        <v>1837.6999999999998</v>
-      </c>
-      <c r="T7" s="9">
-        <f t="shared" si="11"/>
         <v>1969.3999999999996</v>
       </c>
       <c r="U7" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>2285.3000000000006</v>
       </c>
       <c r="V7" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>2241.8000000000002</v>
       </c>
       <c r="W7" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>3062.2000000000003</v>
       </c>
       <c r="X7" s="9">
-        <f t="shared" si="11"/>
-        <v>3605.7542999999996</v>
+        <f t="shared" si="10"/>
+        <v>3802.2181199999995</v>
       </c>
       <c r="Y7" s="9">
         <f>Y5*0.58</f>
-        <v>6085.384939999999</v>
+        <v>5367.5765919999994</v>
       </c>
       <c r="Z7" s="9">
-        <f t="shared" ref="Z7:AG7" si="12">Z5*0.58</f>
-        <v>5659.4079941999998</v>
+        <f t="shared" ref="Z7:AG7" si="11">Z5*0.58</f>
+        <v>6172.7130807999993</v>
       </c>
       <c r="AA7" s="9">
-        <f t="shared" si="12"/>
-        <v>5772.5961540839999</v>
+        <f t="shared" si="11"/>
+        <v>6296.167342415999</v>
       </c>
       <c r="AB7" s="9">
-        <f t="shared" si="12"/>
-        <v>5830.3221156248401</v>
+        <f t="shared" si="11"/>
+        <v>6359.1290158401589</v>
       </c>
       <c r="AC7" s="9">
-        <f t="shared" si="12"/>
-        <v>5888.6253367810887</v>
+        <f t="shared" si="11"/>
+        <v>6422.7203059985613</v>
       </c>
       <c r="AD7" s="9">
-        <f t="shared" si="12"/>
-        <v>5947.5115901488989</v>
+        <f t="shared" si="11"/>
+        <v>6486.9475090585465</v>
       </c>
       <c r="AE7" s="9">
-        <f t="shared" si="12"/>
-        <v>6006.9867060503884</v>
+        <f t="shared" si="11"/>
+        <v>6551.8169841491317</v>
       </c>
       <c r="AF7" s="9">
-        <f t="shared" si="12"/>
-        <v>6067.0565731108918</v>
+        <f t="shared" si="11"/>
+        <v>6617.3351539906234</v>
       </c>
       <c r="AG7" s="9">
-        <f t="shared" si="12"/>
-        <v>6127.7271388420013</v>
+        <f t="shared" si="11"/>
+        <v>6683.5085055305299</v>
       </c>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.3">
@@ -1544,16 +1538,14 @@
         <v>408.8</v>
       </c>
       <c r="L8" s="6">
-        <f>L5*0.27</f>
-        <v>410.25609000000003</v>
+        <v>536.6</v>
       </c>
       <c r="M8" s="6">
-        <f t="shared" ref="M8:N8" si="13">M5*0.27</f>
-        <v>408.99789000000004</v>
+        <v>433.2</v>
       </c>
       <c r="N8" s="6">
-        <f t="shared" si="13"/>
-        <v>441.10332000000005</v>
+        <f>N5*0.25</f>
+        <v>408.42900000000003</v>
       </c>
       <c r="S8" s="6">
         <v>445</v>
@@ -1571,8 +1563,8 @@
         <v>1683.7</v>
       </c>
       <c r="X8" s="6">
-        <f t="shared" ref="X8:X13" si="14">SUM(K8:N8)</f>
-        <v>1669.1573000000003</v>
+        <f t="shared" ref="X8:X13" si="12">SUM(K8:N8)</f>
+        <v>1787.0290000000002</v>
       </c>
       <c r="Y8" s="6"/>
       <c r="Z8" s="6"/>
@@ -1616,16 +1608,14 @@
         <v>261.39999999999998</v>
       </c>
       <c r="L9" s="6">
-        <f>H9*1.15</f>
-        <v>283.70499999999998</v>
+        <v>268</v>
       </c>
       <c r="M9" s="6">
-        <f>I9*1.13</f>
-        <v>272.21699999999998</v>
+        <v>282.7</v>
       </c>
       <c r="N9" s="6">
-        <f>J9*1.07</f>
-        <v>318.64600000000002</v>
+        <f>J9*1.02</f>
+        <v>303.75600000000003</v>
       </c>
       <c r="S9" s="6">
         <v>317.3</v>
@@ -1643,8 +1633,8 @@
         <v>1005.2</v>
       </c>
       <c r="X9" s="6">
-        <f t="shared" si="14"/>
-        <v>1135.9680000000001</v>
+        <f t="shared" si="12"/>
+        <v>1115.856</v>
       </c>
       <c r="Y9" s="6"/>
       <c r="Z9" s="6"/>
@@ -1688,15 +1678,13 @@
         <v>207</v>
       </c>
       <c r="L10" s="6">
-        <f>H10*0.95</f>
-        <v>240.35</v>
+        <v>225</v>
       </c>
       <c r="M10" s="6">
-        <f t="shared" ref="M10:N10" si="15">I10*1.02</f>
-        <v>193.392</v>
+        <v>218.6</v>
       </c>
       <c r="N10" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="N10" si="13">J10*1.02</f>
         <v>234.804</v>
       </c>
       <c r="S10" s="6">
@@ -1715,8 +1703,8 @@
         <v>883.3</v>
       </c>
       <c r="X10" s="6">
-        <f t="shared" si="14"/>
-        <v>875.54599999999994</v>
+        <f t="shared" si="12"/>
+        <v>885.404</v>
       </c>
       <c r="Y10" s="6"/>
       <c r="Z10" s="6"/>
@@ -1760,13 +1748,13 @@
         <v>50.4</v>
       </c>
       <c r="L11" s="6">
-        <v>50</v>
+        <v>48.8</v>
       </c>
       <c r="M11" s="6">
-        <v>50</v>
+        <v>49.1</v>
       </c>
       <c r="N11" s="6">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S11" s="6">
         <v>55.6</v>
@@ -1784,8 +1772,8 @@
         <v>229.4</v>
       </c>
       <c r="X11" s="6">
-        <f t="shared" si="14"/>
-        <v>240.4</v>
+        <f t="shared" si="12"/>
+        <v>236.29999999999998</v>
       </c>
       <c r="Y11" s="6"/>
       <c r="Z11" s="6"/>
@@ -1853,7 +1841,7 @@
         <v>3545.2</v>
       </c>
       <c r="X12" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Y12" s="6"/>
@@ -1898,10 +1886,10 @@
         <v>-4.2</v>
       </c>
       <c r="L13" s="6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M13" s="6">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N13" s="6">
         <v>0</v>
@@ -1922,8 +1910,8 @@
         <v>106.5</v>
       </c>
       <c r="X13" s="6">
-        <f t="shared" si="14"/>
-        <v>-4.2</v>
+        <f t="shared" si="12"/>
+        <v>-3.5000000000000004</v>
       </c>
       <c r="Y13" s="6"/>
       <c r="Z13" s="6"/>
@@ -1940,112 +1928,112 @@
         <v>22</v>
       </c>
       <c r="C14" s="6">
-        <f t="shared" ref="C14:K14" si="16">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="14">SUM(C8:C13)</f>
         <v>883.5</v>
       </c>
       <c r="D14" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>959.09999999999991</v>
       </c>
       <c r="E14" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>807.6</v>
       </c>
       <c r="F14" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>3182.2</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>956</v>
       </c>
       <c r="H14" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1025.0999999999999</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>892</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4580.2000000000007</v>
       </c>
       <c r="K14" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>923.4</v>
       </c>
       <c r="L14" s="6">
-        <f t="shared" ref="L14" si="17">SUM(L8:L13)</f>
-        <v>984.31109000000004</v>
+        <f t="shared" ref="L14" si="15">SUM(L8:L13)</f>
+        <v>1078.4999999999998</v>
       </c>
       <c r="M14" s="6">
-        <f t="shared" ref="M14" si="18">SUM(M8:M13)</f>
-        <v>924.60689000000002</v>
+        <f t="shared" ref="M14" si="16">SUM(M8:M13)</f>
+        <v>984.2</v>
       </c>
       <c r="N14" s="6">
-        <f t="shared" ref="N14" si="19">SUM(N8:N13)</f>
-        <v>1084.55332</v>
+        <f t="shared" ref="N14" si="17">SUM(N8:N13)</f>
+        <v>1034.989</v>
       </c>
       <c r="S14" s="6">
-        <f t="shared" ref="S14:X14" si="20">SUM(S8:S13)</f>
+        <f t="shared" ref="S14:X14" si="18">SUM(S8:S13)</f>
         <v>1208.2999999999997</v>
       </c>
       <c r="T14" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1495.8</v>
       </c>
       <c r="U14" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>3450.5</v>
       </c>
       <c r="V14" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>5832.4</v>
       </c>
       <c r="W14" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>7453.2999999999993</v>
       </c>
       <c r="X14" s="6">
-        <f t="shared" si="20"/>
-        <v>3916.8713000000007</v>
+        <f t="shared" si="18"/>
+        <v>4021.0890000000004</v>
       </c>
       <c r="Y14" s="6">
         <f>X14*1.1</f>
-        <v>4308.558430000001</v>
+        <v>4423.197900000001</v>
       </c>
       <c r="Z14" s="6">
         <f>Y14*0.95</f>
-        <v>4093.1305085000008</v>
+        <v>4202.0380050000003</v>
       </c>
       <c r="AA14" s="6">
         <f>Z14*1.02</f>
-        <v>4174.9931186700005</v>
+        <v>4286.0787651000001</v>
       </c>
       <c r="AB14" s="6">
         <f>AA14*1.01</f>
-        <v>4216.743049856701</v>
+        <v>4328.9395527510005</v>
       </c>
       <c r="AC14" s="6">
-        <f t="shared" ref="AC14:AG14" si="21">AB14*1.01</f>
-        <v>4258.9104803552682</v>
+        <f t="shared" ref="AC14:AG14" si="19">AB14*1.01</f>
+        <v>4372.2289482785109</v>
       </c>
       <c r="AD14" s="6">
-        <f t="shared" si="21"/>
-        <v>4301.499585158821</v>
+        <f t="shared" si="19"/>
+        <v>4415.9512377612964</v>
       </c>
       <c r="AE14" s="6">
-        <f t="shared" si="21"/>
-        <v>4344.5145810104095</v>
+        <f t="shared" si="19"/>
+        <v>4460.1107501389097</v>
       </c>
       <c r="AF14" s="6">
-        <f t="shared" si="21"/>
-        <v>4387.9597268205134</v>
+        <f t="shared" si="19"/>
+        <v>4504.7118576402991</v>
       </c>
       <c r="AG14" s="6">
-        <f t="shared" si="21"/>
-        <v>4431.839324088719</v>
+        <f t="shared" si="19"/>
+        <v>4549.7589762167017</v>
       </c>
     </row>
     <row r="15" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2053,112 +2041,112 @@
         <v>25</v>
       </c>
       <c r="C15" s="9">
-        <f t="shared" ref="C15:K15" si="22">C7-C14</f>
+        <f t="shared" ref="C15:K15" si="20">C7-C14</f>
         <v>-204.30000000000018</v>
       </c>
       <c r="D15" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-543.70000000000005</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-129.50000000000011</v>
       </c>
       <c r="F15" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-2713.1</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-184.89999999999998</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-297.19999999999982</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-132.10000000000002</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-3776.9000000000005</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>21.600000000000023</v>
       </c>
       <c r="L15" s="9">
-        <f t="shared" ref="L15" si="23">L7-L14</f>
-        <v>-118.21490000000006</v>
+        <f t="shared" ref="L15" si="21">L7-L14</f>
+        <v>-97.999999999999545</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" ref="M15" si="24">M7-M14</f>
-        <v>-61.166900000000055</v>
+        <f t="shared" ref="M15" si="22">M7-M14</f>
+        <v>-38.700000000000045</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" ref="N15" si="25">N7-N14</f>
-        <v>-153.33519999999999</v>
+        <f t="shared" ref="N15" si="23">N7-N14</f>
+        <v>-103.77088000000003</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" ref="S15:X15" si="26">S7-S14</f>
+        <f t="shared" ref="S15:X15" si="24">S7-S14</f>
         <v>629.40000000000009</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>473.59999999999968</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>-1165.1999999999994</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>-3590.5999999999995</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>-4391.0999999999985</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" si="26"/>
-        <v>-311.1170000000011</v>
+        <f t="shared" si="24"/>
+        <v>-218.87088000000085</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" ref="Y15:AG15" si="27">Y7-Y14</f>
-        <v>1776.8265099999981</v>
+        <f t="shared" ref="Y15:AG15" si="25">Y7-Y14</f>
+        <v>944.37869199999841</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" si="27"/>
-        <v>1566.277485699999</v>
+        <f t="shared" si="25"/>
+        <v>1970.6750757999989</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" si="27"/>
-        <v>1597.6030354139994</v>
+        <f t="shared" si="25"/>
+        <v>2010.0885773159989</v>
       </c>
       <c r="AB15" s="9">
-        <f t="shared" si="27"/>
-        <v>1613.5790657681391</v>
+        <f t="shared" si="25"/>
+        <v>2030.1894630891584</v>
       </c>
       <c r="AC15" s="9">
-        <f t="shared" si="27"/>
-        <v>1629.7148564258205</v>
+        <f t="shared" si="25"/>
+        <v>2050.4913577200505</v>
       </c>
       <c r="AD15" s="9">
-        <f t="shared" si="27"/>
-        <v>1646.0120049900779</v>
+        <f t="shared" si="25"/>
+        <v>2070.9962712972501</v>
       </c>
       <c r="AE15" s="9">
-        <f t="shared" si="27"/>
-        <v>1662.4721250399789</v>
+        <f t="shared" si="25"/>
+        <v>2091.706234010222</v>
       </c>
       <c r="AF15" s="9">
-        <f t="shared" si="27"/>
-        <v>1679.0968462903784</v>
+        <f t="shared" si="25"/>
+        <v>2112.6232963503244</v>
       </c>
       <c r="AG15" s="9">
-        <f t="shared" si="27"/>
-        <v>1695.8878147532823</v>
+        <f t="shared" si="25"/>
+        <v>2133.7495293138281</v>
       </c>
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.3">
@@ -2193,13 +2181,13 @@
         <v>35.4</v>
       </c>
       <c r="L16" s="6">
-        <v>35</v>
+        <v>17.5</v>
       </c>
       <c r="M16" s="6">
-        <v>35</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="N16" s="6">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="S16" s="6">
         <v>-8.8000000000000007</v>
@@ -2217,8 +2205,8 @@
         <v>93.3</v>
       </c>
       <c r="X16" s="6">
-        <f t="shared" ref="X16:X17" si="28">SUM(K16:N16)</f>
-        <v>140.4</v>
+        <f t="shared" ref="X16:X17" si="26">SUM(K16:N16)</f>
+        <v>96</v>
       </c>
       <c r="Y16" s="6"/>
       <c r="Z16" s="6"/>
@@ -2286,7 +2274,7 @@
         <v>6.9</v>
       </c>
       <c r="X17" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Y17" s="6"/>
@@ -2304,52 +2292,52 @@
         <v>23</v>
       </c>
       <c r="C18" s="6">
-        <f t="shared" ref="C18:K18" si="29">SUM(C16:C17)</f>
+        <f t="shared" ref="C18:K18" si="27">SUM(C16:C17)</f>
         <v>24.599999999999998</v>
       </c>
       <c r="D18" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>33.300000000000004</v>
       </c>
       <c r="E18" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>22.8</v>
       </c>
       <c r="F18" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>31.5</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>27.3</v>
       </c>
       <c r="H18" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>27.099999999999998</v>
       </c>
       <c r="I18" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>20.8</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>25</v>
       </c>
       <c r="K18" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>35.4</v>
       </c>
       <c r="L18" s="6">
-        <f t="shared" ref="L18" si="30">SUM(L16:L17)</f>
-        <v>35</v>
+        <f t="shared" ref="L18" si="28">SUM(L16:L17)</f>
+        <v>17.5</v>
       </c>
       <c r="M18" s="6">
-        <f t="shared" ref="M18" si="31">SUM(M16:M17)</f>
-        <v>35</v>
+        <f t="shared" ref="M18" si="29">SUM(M16:M17)</f>
+        <v>17.100000000000001</v>
       </c>
       <c r="N18" s="6">
-        <f t="shared" ref="N18" si="32">SUM(N16:N17)</f>
-        <v>35</v>
+        <f t="shared" ref="N18" si="30">SUM(N16:N17)</f>
+        <v>26</v>
       </c>
       <c r="S18" s="6">
         <f>SUM(S16:S17)</f>
@@ -2360,56 +2348,56 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="U18" s="6">
-        <f t="shared" ref="U18:X18" si="33">SUM(U16:U17)</f>
+        <f t="shared" ref="U18:X18" si="31">SUM(U16:U17)</f>
         <v>172.9</v>
       </c>
       <c r="V18" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>112.19999999999999</v>
       </c>
       <c r="W18" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>100.2</v>
       </c>
       <c r="X18" s="6">
-        <f t="shared" si="33"/>
-        <v>140.4</v>
+        <f t="shared" si="31"/>
+        <v>96</v>
       </c>
       <c r="Y18" s="6">
         <f>X18*1.02</f>
-        <v>143.208</v>
+        <v>97.92</v>
       </c>
       <c r="Z18" s="6">
-        <f t="shared" ref="Z18:AG18" si="34">Y18*1.02</f>
-        <v>146.07216</v>
+        <f t="shared" ref="Z18:AG18" si="32">Y18*1.02</f>
+        <v>99.878399999999999</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="34"/>
-        <v>148.9936032</v>
+        <f t="shared" si="32"/>
+        <v>101.875968</v>
       </c>
       <c r="AB18" s="6">
-        <f t="shared" si="34"/>
-        <v>151.973475264</v>
+        <f t="shared" si="32"/>
+        <v>103.91348736</v>
       </c>
       <c r="AC18" s="6">
-        <f t="shared" si="34"/>
-        <v>155.01294476928001</v>
+        <f t="shared" si="32"/>
+        <v>105.9917571072</v>
       </c>
       <c r="AD18" s="6">
-        <f t="shared" si="34"/>
-        <v>158.1132036646656</v>
+        <f t="shared" si="32"/>
+        <v>108.111592249344</v>
       </c>
       <c r="AE18" s="6">
-        <f t="shared" si="34"/>
-        <v>161.27546773795891</v>
+        <f t="shared" si="32"/>
+        <v>110.27382409433088</v>
       </c>
       <c r="AF18" s="6">
-        <f t="shared" si="34"/>
-        <v>164.50097709271807</v>
+        <f t="shared" si="32"/>
+        <v>112.4793005762175</v>
       </c>
       <c r="AG18" s="6">
-        <f t="shared" si="34"/>
-        <v>167.79099663457245</v>
+        <f t="shared" si="32"/>
+        <v>114.72888658774185</v>
       </c>
     </row>
     <row r="19" spans="2:139" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2417,52 +2405,52 @@
         <v>26</v>
       </c>
       <c r="C19" s="9">
-        <f t="shared" ref="C19:K19" si="35">C15-C18</f>
+        <f t="shared" ref="C19:K19" si="33">C15-C18</f>
         <v>-228.90000000000018</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-577</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-152.30000000000013</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-2744.6</v>
       </c>
       <c r="G19" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-212.2</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-324.29999999999984</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-152.90000000000003</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-3801.9000000000005</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-13.799999999999976</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" ref="L19" si="36">L15-L18</f>
-        <v>-153.21490000000006</v>
+        <f t="shared" ref="L19" si="34">L15-L18</f>
+        <v>-115.49999999999955</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" ref="M19" si="37">M15-M18</f>
-        <v>-96.166900000000055</v>
+        <f t="shared" ref="M19" si="35">M15-M18</f>
+        <v>-55.800000000000047</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" ref="N19" si="38">N15-N18</f>
-        <v>-188.33519999999999</v>
+        <f t="shared" ref="N19" si="36">N15-N18</f>
+        <v>-129.77088000000003</v>
       </c>
       <c r="S19" s="9">
         <f>S15-S18</f>
@@ -2473,56 +2461,56 @@
         <v>465.39999999999969</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" ref="U19:W19" si="39">U15-U18</f>
+        <f t="shared" ref="U19:W19" si="37">U15-U18</f>
         <v>-1338.0999999999995</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>-3702.7999999999993</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>-4491.2999999999984</v>
       </c>
       <c r="X19" s="9">
         <f>X15-X18</f>
-        <v>-451.51700000000108</v>
+        <v>-314.87088000000085</v>
       </c>
       <c r="Y19" s="9">
         <f>Y15-Y18</f>
-        <v>1633.618509999998</v>
+        <v>846.45869199999845</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" ref="Z19:AG19" si="40">Z15-Z18</f>
-        <v>1420.2053256999991</v>
+        <f t="shared" ref="Z19:AG19" si="38">Z15-Z18</f>
+        <v>1870.7966757999989</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="40"/>
-        <v>1448.6094322139993</v>
+        <f t="shared" si="38"/>
+        <v>1908.2126093159989</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="40"/>
-        <v>1461.6055905041392</v>
+        <f t="shared" si="38"/>
+        <v>1926.2759757291583</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" si="40"/>
-        <v>1474.7019116565405</v>
+        <f t="shared" si="38"/>
+        <v>1944.4996006128504</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" si="40"/>
-        <v>1487.8988013254123</v>
+        <f t="shared" si="38"/>
+        <v>1962.884679047906</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="40"/>
-        <v>1501.19665730202</v>
+        <f t="shared" si="38"/>
+        <v>1981.4324099158912</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" si="40"/>
-        <v>1514.5958691976602</v>
+        <f t="shared" si="38"/>
+        <v>2000.1439957741068</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="40"/>
-        <v>1528.09681811871</v>
+        <f t="shared" si="38"/>
+        <v>2019.0206427260862</v>
       </c>
     </row>
     <row r="20" spans="2:139" x14ac:dyDescent="0.3">
@@ -2557,16 +2545,14 @@
         <v>-1.9</v>
       </c>
       <c r="L20" s="6">
-        <f>L19*0.1</f>
-        <v>-15.321490000000006</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="M20" s="6">
-        <f t="shared" ref="M20:N20" si="41">M19*0.1</f>
-        <v>-9.6166900000000055</v>
+        <v>37.1</v>
       </c>
       <c r="N20" s="6">
-        <f t="shared" si="41"/>
-        <v>-18.83352</v>
+        <f t="shared" ref="N20" si="39">N19*0.1</f>
+        <v>-12.977088000000004</v>
       </c>
       <c r="S20" s="6">
         <v>88.9</v>
@@ -2584,44 +2570,44 @@
         <v>-12.4</v>
       </c>
       <c r="X20" s="6">
-        <f t="shared" ref="X20" si="42">SUM(K20:N20)</f>
-        <v>-45.671700000000016</v>
+        <f t="shared" ref="X20" si="40">SUM(K20:N20)</f>
+        <v>40.622911999999999</v>
       </c>
       <c r="Y20" s="6">
         <f>Y19*0.15</f>
-        <v>245.04277649999969</v>
+        <v>126.96880379999976</v>
       </c>
       <c r="Z20" s="6">
-        <f t="shared" ref="Z20:AG20" si="43">Z19*0.15</f>
-        <v>213.03079885499986</v>
+        <f t="shared" ref="Z20:AG20" si="41">Z19*0.15</f>
+        <v>280.6195013699998</v>
       </c>
       <c r="AA20" s="6">
-        <f t="shared" si="43"/>
-        <v>217.29141483209989</v>
+        <f t="shared" si="41"/>
+        <v>286.23189139739981</v>
       </c>
       <c r="AB20" s="6">
-        <f t="shared" si="43"/>
-        <v>219.24083857562087</v>
+        <f t="shared" si="41"/>
+        <v>288.94139635937375</v>
       </c>
       <c r="AC20" s="6">
-        <f t="shared" si="43"/>
-        <v>221.20528674848106</v>
+        <f t="shared" si="41"/>
+        <v>291.67494009192757</v>
       </c>
       <c r="AD20" s="6">
-        <f t="shared" si="43"/>
-        <v>223.18482019881182</v>
+        <f t="shared" si="41"/>
+        <v>294.43270185718592</v>
       </c>
       <c r="AE20" s="6">
-        <f t="shared" si="43"/>
-        <v>225.17949859530299</v>
+        <f t="shared" si="41"/>
+        <v>297.21486148738364</v>
       </c>
       <c r="AF20" s="6">
-        <f t="shared" si="43"/>
-        <v>227.18938037964904</v>
+        <f t="shared" si="41"/>
+        <v>300.02159936611599</v>
       </c>
       <c r="AG20" s="6">
-        <f t="shared" si="43"/>
-        <v>229.21452271780649</v>
+        <f t="shared" si="41"/>
+        <v>302.8530964089129</v>
       </c>
     </row>
     <row r="21" spans="2:139" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2629,536 +2615,536 @@
         <v>28</v>
       </c>
       <c r="C21" s="9">
-        <f t="shared" ref="C21:K21" si="44">C19-C20</f>
+        <f t="shared" ref="C21:K21" si="42">C19-C20</f>
         <v>-206.00000000000017</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-543.6</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-91.600000000000122</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-2903</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-262</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-365.49999999999983</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-125.20000000000003</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-3726.2000000000007</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-11.899999999999975</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" ref="L21" si="45">L19-L20</f>
-        <v>-137.89341000000005</v>
+        <f t="shared" ref="L21" si="43">L19-L20</f>
+        <v>-133.89999999999955</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" ref="M21" si="46">M19-M20</f>
-        <v>-86.55021000000005</v>
+        <f t="shared" ref="M21" si="44">M19-M20</f>
+        <v>-92.900000000000048</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" ref="N21" si="47">N19-N20</f>
-        <v>-169.50167999999999</v>
+        <f t="shared" ref="N21" si="45">N19-N20</f>
+        <v>-116.79379200000002</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21:Y21" si="48">S19-S20</f>
+        <f t="shared" ref="S21:Y21" si="46">S19-S20</f>
         <v>588.90000000000009</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>417.99999999999972</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>-1124.6999999999994</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>-3744.1999999999994</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>-4478.8999999999987</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="48"/>
-        <v>-405.84530000000109</v>
+        <f t="shared" si="46"/>
+        <v>-355.49379200000084</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="48"/>
-        <v>1388.5757334999983</v>
+        <f t="shared" si="46"/>
+        <v>719.48988819999863</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" ref="Z21:AG21" si="49">Z19-Z20</f>
-        <v>1207.1745268449993</v>
+        <f t="shared" ref="Z21:AG21" si="47">Z19-Z20</f>
+        <v>1590.177174429999</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="49"/>
-        <v>1231.3180173818994</v>
+        <f t="shared" si="47"/>
+        <v>1621.9807179185991</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="49"/>
-        <v>1242.3647519285182</v>
+        <f t="shared" si="47"/>
+        <v>1637.3345793697845</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="49"/>
-        <v>1253.4966249080594</v>
+        <f t="shared" si="47"/>
+        <v>1652.8246605209229</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="49"/>
-        <v>1264.7139811266004</v>
+        <f t="shared" si="47"/>
+        <v>1668.4519771907201</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="49"/>
-        <v>1276.0171587067171</v>
+        <f t="shared" si="47"/>
+        <v>1684.2175484285076</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="49"/>
-        <v>1287.4064888180112</v>
+        <f t="shared" si="47"/>
+        <v>1700.1223964079909</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="49"/>
-        <v>1298.8822954009036</v>
+        <f t="shared" si="47"/>
+        <v>1716.1675463171732</v>
       </c>
       <c r="AH21" s="2">
         <f>AG21*(1+$AK$28)</f>
-        <v>1285.8934724468945</v>
+        <v>1699.0058708540014</v>
       </c>
       <c r="AI21" s="2">
-        <f t="shared" ref="AI21:CT21" si="50">AH21*(1+$AK$28)</f>
-        <v>1273.0345377224255</v>
+        <f t="shared" ref="AI21:CT21" si="48">AH21*(1+$AK$28)</f>
+        <v>1682.0158121454613</v>
       </c>
       <c r="AJ21" s="2">
-        <f t="shared" si="50"/>
-        <v>1260.3041923452013</v>
+        <f t="shared" si="48"/>
+        <v>1665.1956540240067</v>
       </c>
       <c r="AK21" s="2">
-        <f t="shared" si="50"/>
-        <v>1247.7011504217492</v>
+        <f t="shared" si="48"/>
+        <v>1648.5436974837667</v>
       </c>
       <c r="AL21" s="2">
-        <f t="shared" si="50"/>
-        <v>1235.2241389175317</v>
+        <f t="shared" si="48"/>
+        <v>1632.0582605089289</v>
       </c>
       <c r="AM21" s="2">
-        <f t="shared" si="50"/>
-        <v>1222.8718975283564</v>
+        <f t="shared" si="48"/>
+        <v>1615.7376779038395</v>
       </c>
       <c r="AN21" s="2">
-        <f t="shared" si="50"/>
-        <v>1210.6431785530729</v>
+        <f t="shared" si="48"/>
+        <v>1599.5803011248011</v>
       </c>
       <c r="AO21" s="2">
-        <f t="shared" si="50"/>
-        <v>1198.5367467675421</v>
+        <f t="shared" si="48"/>
+        <v>1583.5844981135531</v>
       </c>
       <c r="AP21" s="2">
-        <f t="shared" si="50"/>
-        <v>1186.5513792998668</v>
+        <f t="shared" si="48"/>
+        <v>1567.7486531324175</v>
       </c>
       <c r="AQ21" s="2">
-        <f t="shared" si="50"/>
-        <v>1174.6858655068681</v>
+        <f t="shared" si="48"/>
+        <v>1552.0711666010934</v>
       </c>
       <c r="AR21" s="2">
-        <f t="shared" si="50"/>
-        <v>1162.9390068517994</v>
+        <f t="shared" si="48"/>
+        <v>1536.5504549350824</v>
       </c>
       <c r="AS21" s="2">
-        <f t="shared" si="50"/>
-        <v>1151.3096167832814</v>
+        <f t="shared" si="48"/>
+        <v>1521.1849503857316</v>
       </c>
       <c r="AT21" s="2">
-        <f t="shared" si="50"/>
-        <v>1139.7965206154486</v>
+        <f t="shared" si="48"/>
+        <v>1505.9731008818742</v>
       </c>
       <c r="AU21" s="2">
-        <f t="shared" si="50"/>
-        <v>1128.398555409294</v>
+        <f t="shared" si="48"/>
+        <v>1490.9133698730554</v>
       </c>
       <c r="AV21" s="2">
-        <f t="shared" si="50"/>
-        <v>1117.1145698552011</v>
+        <f t="shared" si="48"/>
+        <v>1476.0042361743249</v>
       </c>
       <c r="AW21" s="2">
-        <f t="shared" si="50"/>
-        <v>1105.9434241566491</v>
+        <f t="shared" si="48"/>
+        <v>1461.2441938125817</v>
       </c>
       <c r="AX21" s="2">
-        <f t="shared" si="50"/>
-        <v>1094.8839899150826</v>
+        <f t="shared" si="48"/>
+        <v>1446.6317518744559</v>
       </c>
       <c r="AY21" s="2">
-        <f t="shared" si="50"/>
-        <v>1083.9351500159316</v>
+        <f t="shared" si="48"/>
+        <v>1432.1654343557113</v>
       </c>
       <c r="AZ21" s="2">
-        <f t="shared" si="50"/>
-        <v>1073.0957985157722</v>
+        <f t="shared" si="48"/>
+        <v>1417.8437800121542</v>
       </c>
       <c r="BA21" s="2">
-        <f t="shared" si="50"/>
-        <v>1062.3648405306144</v>
+        <f t="shared" si="48"/>
+        <v>1403.6653422120326</v>
       </c>
       <c r="BB21" s="2">
-        <f t="shared" si="50"/>
-        <v>1051.7411921253083</v>
+        <f t="shared" si="48"/>
+        <v>1389.6286887899123</v>
       </c>
       <c r="BC21" s="2">
-        <f t="shared" si="50"/>
-        <v>1041.2237802040552</v>
+        <f t="shared" si="48"/>
+        <v>1375.7324019020132</v>
       </c>
       <c r="BD21" s="2">
-        <f t="shared" si="50"/>
-        <v>1030.8115424020145</v>
+        <f t="shared" si="48"/>
+        <v>1361.975077882993</v>
       </c>
       <c r="BE21" s="2">
-        <f t="shared" si="50"/>
-        <v>1020.5034269779944</v>
+        <f t="shared" si="48"/>
+        <v>1348.3553271041631</v>
       </c>
       <c r="BF21" s="2">
-        <f t="shared" si="50"/>
-        <v>1010.2983927082145</v>
+        <f t="shared" si="48"/>
+        <v>1334.8717738331213</v>
       </c>
       <c r="BG21" s="2">
-        <f t="shared" si="50"/>
-        <v>1000.1954087811323</v>
+        <f t="shared" si="48"/>
+        <v>1321.52305609479</v>
       </c>
       <c r="BH21" s="2">
-        <f t="shared" si="50"/>
-        <v>990.19345469332097</v>
+        <f t="shared" si="48"/>
+        <v>1308.3078255338421</v>
       </c>
       <c r="BI21" s="2">
-        <f t="shared" si="50"/>
-        <v>980.29152014638771</v>
+        <f t="shared" si="48"/>
+        <v>1295.2247472785036</v>
       </c>
       <c r="BJ21" s="2">
-        <f t="shared" si="50"/>
-        <v>970.48860494492385</v>
+        <f t="shared" si="48"/>
+        <v>1282.2724998057186</v>
       </c>
       <c r="BK21" s="2">
-        <f t="shared" si="50"/>
-        <v>960.78371889547464</v>
+        <f t="shared" si="48"/>
+        <v>1269.4497748076615</v>
       </c>
       <c r="BL21" s="2">
-        <f t="shared" si="50"/>
-        <v>951.17588170651993</v>
+        <f t="shared" si="48"/>
+        <v>1256.7552770595848</v>
       </c>
       <c r="BM21" s="2">
-        <f t="shared" si="50"/>
-        <v>941.66412288945469</v>
+        <f t="shared" si="48"/>
+        <v>1244.1877242889889</v>
       </c>
       <c r="BN21" s="2">
-        <f t="shared" si="50"/>
-        <v>932.24748166056008</v>
+        <f t="shared" si="48"/>
+        <v>1231.745847046099</v>
       </c>
       <c r="BO21" s="2">
-        <f t="shared" si="50"/>
-        <v>922.92500684395452</v>
+        <f t="shared" si="48"/>
+        <v>1219.4283885756381</v>
       </c>
       <c r="BP21" s="2">
-        <f t="shared" si="50"/>
-        <v>913.69575677551495</v>
+        <f t="shared" si="48"/>
+        <v>1207.2341046898816</v>
       </c>
       <c r="BQ21" s="2">
-        <f t="shared" si="50"/>
-        <v>904.55879920775976</v>
+        <f t="shared" si="48"/>
+        <v>1195.1617636429828</v>
       </c>
       <c r="BR21" s="2">
-        <f t="shared" si="50"/>
-        <v>895.51321121568219</v>
+        <f t="shared" si="48"/>
+        <v>1183.210146006553</v>
       </c>
       <c r="BS21" s="2">
-        <f t="shared" si="50"/>
-        <v>886.55807910352542</v>
+        <f t="shared" si="48"/>
+        <v>1171.3780445464874</v>
       </c>
       <c r="BT21" s="2">
-        <f t="shared" si="50"/>
-        <v>877.6924983124901</v>
+        <f t="shared" si="48"/>
+        <v>1159.6642641010226</v>
       </c>
       <c r="BU21" s="2">
-        <f t="shared" si="50"/>
-        <v>868.9155733293652</v>
+        <f t="shared" si="48"/>
+        <v>1148.0676214600123</v>
       </c>
       <c r="BV21" s="2">
-        <f t="shared" si="50"/>
-        <v>860.22641759607154</v>
+        <f t="shared" si="48"/>
+        <v>1136.5869452454122</v>
       </c>
       <c r="BW21" s="2">
-        <f t="shared" si="50"/>
-        <v>851.62415342011082</v>
+        <f t="shared" si="48"/>
+        <v>1125.2210757929581</v>
       </c>
       <c r="BX21" s="2">
-        <f t="shared" si="50"/>
-        <v>843.10791188590974</v>
+        <f t="shared" si="48"/>
+        <v>1113.9688650350286</v>
       </c>
       <c r="BY21" s="2">
-        <f t="shared" si="50"/>
-        <v>834.67683276705066</v>
+        <f t="shared" si="48"/>
+        <v>1102.8291763846782</v>
       </c>
       <c r="BZ21" s="2">
-        <f t="shared" si="50"/>
-        <v>826.33006443938018</v>
+        <f t="shared" si="48"/>
+        <v>1091.8008846208315</v>
       </c>
       <c r="CA21" s="2">
-        <f t="shared" si="50"/>
-        <v>818.0667637949864</v>
+        <f t="shared" si="48"/>
+        <v>1080.8828757746232</v>
       </c>
       <c r="CB21" s="2">
-        <f t="shared" si="50"/>
-        <v>809.88609615703649</v>
+        <f t="shared" si="48"/>
+        <v>1070.0740470168771</v>
       </c>
       <c r="CC21" s="2">
-        <f t="shared" si="50"/>
-        <v>801.78723519546611</v>
+        <f t="shared" si="48"/>
+        <v>1059.3733065467084</v>
       </c>
       <c r="CD21" s="2">
-        <f t="shared" si="50"/>
-        <v>793.76936284351143</v>
+        <f t="shared" si="48"/>
+        <v>1048.7795734812412</v>
       </c>
       <c r="CE21" s="2">
-        <f t="shared" si="50"/>
-        <v>785.83166921507632</v>
+        <f t="shared" si="48"/>
+        <v>1038.2917777464288</v>
       </c>
       <c r="CF21" s="2">
-        <f t="shared" si="50"/>
-        <v>777.97335252292555</v>
+        <f t="shared" si="48"/>
+        <v>1027.9088599689644</v>
       </c>
       <c r="CG21" s="2">
-        <f t="shared" si="50"/>
-        <v>770.19361899769626</v>
+        <f t="shared" si="48"/>
+        <v>1017.6297713692747</v>
       </c>
       <c r="CH21" s="2">
-        <f t="shared" si="50"/>
-        <v>762.49168280771926</v>
+        <f t="shared" si="48"/>
+        <v>1007.453473655582</v>
       </c>
       <c r="CI21" s="2">
-        <f t="shared" si="50"/>
-        <v>754.86676597964208</v>
+        <f t="shared" si="48"/>
+        <v>997.37893891902615</v>
       </c>
       <c r="CJ21" s="2">
-        <f t="shared" si="50"/>
-        <v>747.3180983198456</v>
+        <f t="shared" si="48"/>
+        <v>987.40514952983585</v>
       </c>
       <c r="CK21" s="2">
-        <f t="shared" si="50"/>
-        <v>739.84491733664709</v>
+        <f t="shared" si="48"/>
+        <v>977.53109803453754</v>
       </c>
       <c r="CL21" s="2">
-        <f t="shared" si="50"/>
-        <v>732.44646816328066</v>
+        <f t="shared" si="48"/>
+        <v>967.75578705419218</v>
       </c>
       <c r="CM21" s="2">
-        <f t="shared" si="50"/>
-        <v>725.12200348164788</v>
+        <f t="shared" si="48"/>
+        <v>958.07822918365025</v>
       </c>
       <c r="CN21" s="2">
-        <f t="shared" si="50"/>
-        <v>717.87078344683141</v>
+        <f t="shared" si="48"/>
+        <v>948.49744689181375</v>
       </c>
       <c r="CO21" s="2">
-        <f t="shared" si="50"/>
-        <v>710.69207561236306</v>
+        <f t="shared" si="48"/>
+        <v>939.0124724228956</v>
       </c>
       <c r="CP21" s="2">
-        <f t="shared" si="50"/>
-        <v>703.58515485623946</v>
+        <f t="shared" si="48"/>
+        <v>929.62234769866666</v>
       </c>
       <c r="CQ21" s="2">
-        <f t="shared" si="50"/>
-        <v>696.54930330767706</v>
+        <f t="shared" si="48"/>
+        <v>920.32612422167995</v>
       </c>
       <c r="CR21" s="2">
-        <f t="shared" si="50"/>
-        <v>689.5838102746003</v>
+        <f t="shared" si="48"/>
+        <v>911.12286297946309</v>
       </c>
       <c r="CS21" s="2">
-        <f t="shared" si="50"/>
-        <v>682.68797217185431</v>
+        <f t="shared" si="48"/>
+        <v>902.0116343496685</v>
       </c>
       <c r="CT21" s="2">
-        <f t="shared" si="50"/>
-        <v>675.86109245013574</v>
+        <f t="shared" si="48"/>
+        <v>892.99151800617176</v>
       </c>
       <c r="CU21" s="2">
-        <f t="shared" ref="CU21:EI21" si="51">CT21*(1+$AK$28)</f>
-        <v>669.1024815256344</v>
+        <f t="shared" ref="CU21:EI21" si="49">CT21*(1+$AK$28)</f>
+        <v>884.06160282611006</v>
       </c>
       <c r="CV21" s="2">
-        <f t="shared" si="51"/>
-        <v>662.41145671037805</v>
+        <f t="shared" si="49"/>
+        <v>875.22098679784892</v>
       </c>
       <c r="CW21" s="2">
-        <f t="shared" si="51"/>
-        <v>655.78734214327426</v>
+        <f t="shared" si="49"/>
+        <v>866.46877692987039</v>
       </c>
       <c r="CX21" s="2">
-        <f t="shared" si="51"/>
-        <v>649.2294687218415</v>
+        <f t="shared" si="49"/>
+        <v>857.80408916057172</v>
       </c>
       <c r="CY21" s="2">
-        <f t="shared" si="51"/>
-        <v>642.73717403462308</v>
+        <f t="shared" si="49"/>
+        <v>849.226048268966</v>
       </c>
       <c r="CZ21" s="2">
-        <f t="shared" si="51"/>
-        <v>636.30980229427689</v>
+        <f t="shared" si="49"/>
+        <v>840.73378778627637</v>
       </c>
       <c r="DA21" s="2">
-        <f t="shared" si="51"/>
-        <v>629.94670427133417</v>
+        <f t="shared" si="49"/>
+        <v>832.32644990841357</v>
       </c>
       <c r="DB21" s="2">
-        <f t="shared" si="51"/>
-        <v>623.64723722862084</v>
+        <f t="shared" si="49"/>
+        <v>824.00318540932938</v>
       </c>
       <c r="DC21" s="2">
-        <f t="shared" si="51"/>
-        <v>617.41076485633459</v>
+        <f t="shared" si="49"/>
+        <v>815.76315355523604</v>
       </c>
       <c r="DD21" s="2">
-        <f t="shared" si="51"/>
-        <v>611.23665720777126</v>
+        <f t="shared" si="49"/>
+        <v>807.60552201968369</v>
       </c>
       <c r="DE21" s="2">
-        <f t="shared" si="51"/>
-        <v>605.12429063569357</v>
+        <f t="shared" si="49"/>
+        <v>799.52946679948684</v>
       </c>
       <c r="DF21" s="2">
-        <f t="shared" si="51"/>
-        <v>599.07304772933662</v>
+        <f t="shared" si="49"/>
+        <v>791.53417213149191</v>
       </c>
       <c r="DG21" s="2">
-        <f t="shared" si="51"/>
-        <v>593.08231725204325</v>
+        <f t="shared" si="49"/>
+        <v>783.618830410177</v>
       </c>
       <c r="DH21" s="2">
-        <f t="shared" si="51"/>
-        <v>587.15149407952276</v>
+        <f t="shared" si="49"/>
+        <v>775.78264210607517</v>
       </c>
       <c r="DI21" s="2">
-        <f t="shared" si="51"/>
-        <v>581.27997913872753</v>
+        <f t="shared" si="49"/>
+        <v>768.02481568501446</v>
       </c>
       <c r="DJ21" s="2">
-        <f t="shared" si="51"/>
-        <v>575.46717934734022</v>
+        <f t="shared" si="49"/>
+        <v>760.34456752816436</v>
       </c>
       <c r="DK21" s="2">
-        <f t="shared" si="51"/>
-        <v>569.71250755386677</v>
+        <f t="shared" si="49"/>
+        <v>752.74112185288266</v>
       </c>
       <c r="DL21" s="2">
-        <f t="shared" si="51"/>
-        <v>564.01538247832809</v>
+        <f t="shared" si="49"/>
+        <v>745.21371063435379</v>
       </c>
       <c r="DM21" s="2">
-        <f t="shared" si="51"/>
-        <v>558.37522865354481</v>
+        <f t="shared" si="49"/>
+        <v>737.76157352801022</v>
       </c>
       <c r="DN21" s="2">
-        <f t="shared" si="51"/>
-        <v>552.79147636700941</v>
+        <f t="shared" si="49"/>
+        <v>730.38395779273014</v>
       </c>
       <c r="DO21" s="2">
-        <f t="shared" si="51"/>
-        <v>547.26356160333933</v>
+        <f t="shared" si="49"/>
+        <v>723.08011821480284</v>
       </c>
       <c r="DP21" s="2">
-        <f t="shared" si="51"/>
-        <v>541.79092598730597</v>
+        <f t="shared" si="49"/>
+        <v>715.84931703265477</v>
       </c>
       <c r="DQ21" s="2">
-        <f t="shared" si="51"/>
-        <v>536.37301672743286</v>
+        <f t="shared" si="49"/>
+        <v>708.69082386232822</v>
       </c>
       <c r="DR21" s="2">
-        <f t="shared" si="51"/>
-        <v>531.00928656015856</v>
+        <f t="shared" si="49"/>
+        <v>701.60391562370489</v>
       </c>
       <c r="DS21" s="2">
-        <f t="shared" si="51"/>
-        <v>525.69919369455693</v>
+        <f t="shared" si="49"/>
+        <v>694.58787646746782</v>
       </c>
       <c r="DT21" s="2">
-        <f t="shared" si="51"/>
-        <v>520.44220175761131</v>
+        <f t="shared" si="49"/>
+        <v>687.64199770279311</v>
       </c>
       <c r="DU21" s="2">
-        <f t="shared" si="51"/>
-        <v>515.23777974003519</v>
+        <f t="shared" si="49"/>
+        <v>680.76557772576518</v>
       </c>
       <c r="DV21" s="2">
-        <f t="shared" si="51"/>
-        <v>510.08540194263486</v>
+        <f t="shared" si="49"/>
+        <v>673.95792194850753</v>
       </c>
       <c r="DW21" s="2">
-        <f t="shared" si="51"/>
-        <v>504.98454792320848</v>
+        <f t="shared" si="49"/>
+        <v>667.21834272902242</v>
       </c>
       <c r="DX21" s="2">
-        <f t="shared" si="51"/>
-        <v>499.93470244397639</v>
+        <f t="shared" si="49"/>
+        <v>660.54615930173225</v>
       </c>
       <c r="DY21" s="2">
-        <f t="shared" si="51"/>
-        <v>494.93535541953662</v>
+        <f t="shared" si="49"/>
+        <v>653.94069770871488</v>
       </c>
       <c r="DZ21" s="2">
-        <f t="shared" si="51"/>
-        <v>489.98600186534122</v>
+        <f t="shared" si="49"/>
+        <v>647.40129073162768</v>
       </c>
       <c r="EA21" s="2">
-        <f t="shared" si="51"/>
-        <v>485.08614184668778</v>
+        <f t="shared" si="49"/>
+        <v>640.92727782431143</v>
       </c>
       <c r="EB21" s="2">
-        <f t="shared" si="51"/>
-        <v>480.2352804282209</v>
+        <f t="shared" si="49"/>
+        <v>634.51800504606831</v>
       </c>
       <c r="EC21" s="2">
-        <f t="shared" si="51"/>
-        <v>475.43292762393867</v>
+        <f t="shared" si="49"/>
+        <v>628.17282499560758</v>
       </c>
       <c r="ED21" s="2">
-        <f t="shared" si="51"/>
-        <v>470.67859834769928</v>
+        <f t="shared" si="49"/>
+        <v>621.89109674565145</v>
       </c>
       <c r="EE21" s="2">
-        <f t="shared" si="51"/>
-        <v>465.97181236422227</v>
+        <f t="shared" si="49"/>
+        <v>615.67218577819494</v>
       </c>
       <c r="EF21" s="2">
-        <f t="shared" si="51"/>
-        <v>461.31209424058005</v>
+        <f t="shared" si="49"/>
+        <v>609.51546392041303</v>
       </c>
       <c r="EG21" s="2">
-        <f t="shared" si="51"/>
-        <v>456.69897329817422</v>
+        <f t="shared" si="49"/>
+        <v>603.42030928120892</v>
       </c>
       <c r="EH21" s="2">
-        <f t="shared" si="51"/>
-        <v>452.13198356519246</v>
+        <f t="shared" si="49"/>
+        <v>597.38610618839687</v>
       </c>
       <c r="EI21" s="2">
-        <f t="shared" si="51"/>
-        <v>447.61066372954053</v>
+        <f t="shared" si="49"/>
+        <v>591.41224512651286</v>
       </c>
     </row>
     <row r="22" spans="2:139" x14ac:dyDescent="0.3">
@@ -3194,16 +3180,16 @@
         <v>184.5</v>
       </c>
       <c r="L22" s="6">
-        <f t="shared" ref="L22:N22" si="52">184.5</f>
-        <v>184.5</v>
+        <f>184.6</f>
+        <v>184.6</v>
       </c>
       <c r="M22" s="6">
-        <f t="shared" si="52"/>
-        <v>184.5</v>
+        <f>184.6</f>
+        <v>184.6</v>
       </c>
       <c r="N22" s="6">
-        <f t="shared" si="52"/>
-        <v>184.5</v>
+        <f>184.6</f>
+        <v>184.6</v>
       </c>
       <c r="S22" s="6">
         <v>177.4</v>
@@ -3221,44 +3207,44 @@
         <v>177.4</v>
       </c>
       <c r="X22" s="6">
-        <f t="shared" ref="X22:AG22" si="53">184.5</f>
-        <v>184.5</v>
+        <f t="shared" ref="X22:AG22" si="50">184.6</f>
+        <v>184.6</v>
       </c>
       <c r="Y22" s="6">
-        <f t="shared" si="53"/>
-        <v>184.5</v>
+        <f t="shared" si="50"/>
+        <v>184.6</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" si="53"/>
-        <v>184.5</v>
+        <f t="shared" si="50"/>
+        <v>184.6</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="53"/>
-        <v>184.5</v>
+        <f t="shared" si="50"/>
+        <v>184.6</v>
       </c>
       <c r="AB22" s="6">
-        <f t="shared" si="53"/>
-        <v>184.5</v>
+        <f t="shared" si="50"/>
+        <v>184.6</v>
       </c>
       <c r="AC22" s="6">
-        <f t="shared" si="53"/>
-        <v>184.5</v>
+        <f t="shared" si="50"/>
+        <v>184.6</v>
       </c>
       <c r="AD22" s="6">
-        <f t="shared" si="53"/>
-        <v>184.5</v>
+        <f t="shared" si="50"/>
+        <v>184.6</v>
       </c>
       <c r="AE22" s="6">
-        <f t="shared" si="53"/>
-        <v>184.5</v>
+        <f t="shared" si="50"/>
+        <v>184.6</v>
       </c>
       <c r="AF22" s="6">
-        <f t="shared" si="53"/>
-        <v>184.5</v>
+        <f t="shared" si="50"/>
+        <v>184.6</v>
       </c>
       <c r="AG22" s="6">
-        <f t="shared" si="53"/>
-        <v>184.5</v>
+        <f t="shared" si="50"/>
+        <v>184.6</v>
       </c>
     </row>
     <row r="23" spans="2:139" x14ac:dyDescent="0.3">
@@ -3266,112 +3252,112 @@
         <v>29</v>
       </c>
       <c r="C23" s="8">
-        <f t="shared" ref="C23:K23" si="54">C21/C22</f>
+        <f t="shared" ref="C23:K23" si="51">C21/C22</f>
         <v>-1.1612175873731689</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-3.0642615558060879</v>
       </c>
       <c r="E23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-0.51634723788049675</v>
       </c>
       <c r="F23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-16.364148816234497</v>
       </c>
       <c r="G23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-1.4768883878241261</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-2.06031567080045</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-0.70574971815107113</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-21.004509582863587</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-6.4498644986449735E-2</v>
       </c>
       <c r="L23" s="8">
-        <f t="shared" ref="L23" si="55">L21/L22</f>
-        <v>-0.7473897560975612</v>
+        <f t="shared" ref="L23" si="52">L21/L22</f>
+        <v>-0.72535211267605393</v>
       </c>
       <c r="M23" s="8">
-        <f t="shared" ref="M23" si="56">M21/M22</f>
-        <v>-0.46910682926829295</v>
+        <f t="shared" ref="M23" si="53">M21/M22</f>
+        <v>-0.5032502708559049</v>
       </c>
       <c r="N23" s="8">
-        <f t="shared" ref="N23" si="57">N21/N22</f>
-        <v>-0.91870829268292675</v>
+        <f t="shared" ref="N23" si="54">N21/N22</f>
+        <v>-0.63268576381365127</v>
       </c>
       <c r="S23" s="8">
-        <f t="shared" ref="S23:Y23" si="58">S21/S22</f>
+        <f t="shared" ref="S23:Y23" si="55">S21/S22</f>
         <v>3.3196166854565958</v>
       </c>
       <c r="T23" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>2.3562570462232229</v>
       </c>
       <c r="U23" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>-6.3399098083427248</v>
       </c>
       <c r="V23" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>-21.105975197294246</v>
       </c>
       <c r="W23" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>-25.247463359639227</v>
       </c>
       <c r="X23" s="8">
-        <f t="shared" si="58"/>
-        <v>-2.1997035230352364</v>
+        <f t="shared" si="55"/>
+        <v>-1.9257518526543924</v>
       </c>
       <c r="Y23" s="8">
-        <f t="shared" si="58"/>
-        <v>7.526155737127362</v>
+        <f t="shared" si="55"/>
+        <v>3.8975616912242614</v>
       </c>
       <c r="Z23" s="8">
-        <f t="shared" ref="Z23:AG23" si="59">Z21/Z22</f>
-        <v>6.542951365013546</v>
+        <f t="shared" ref="Z23:AG23" si="56">Z21/Z22</f>
+        <v>8.6141775429577407</v>
       </c>
       <c r="AA23" s="8">
-        <f t="shared" si="59"/>
-        <v>6.6738103923138175</v>
+        <f t="shared" si="56"/>
+        <v>8.7864610938168966</v>
       </c>
       <c r="AB23" s="8">
-        <f t="shared" si="59"/>
-        <v>6.733684292295492</v>
+        <f t="shared" si="56"/>
+        <v>8.8696347744842061</v>
       </c>
       <c r="AC23" s="8">
-        <f t="shared" si="59"/>
-        <v>6.7940196471981542</v>
+        <f t="shared" si="56"/>
+        <v>8.9535463733527791</v>
       </c>
       <c r="AD23" s="8">
-        <f t="shared" si="59"/>
-        <v>6.8548183258894326</v>
+        <f t="shared" si="56"/>
+        <v>9.0382013932325034</v>
       </c>
       <c r="AE23" s="8">
-        <f t="shared" si="59"/>
-        <v>6.9160821610120164</v>
+        <f t="shared" si="56"/>
+        <v>9.1236053544339519</v>
       </c>
       <c r="AF23" s="8">
-        <f t="shared" si="59"/>
-        <v>6.9778129475230957</v>
+        <f t="shared" si="56"/>
+        <v>9.209763794192801</v>
       </c>
       <c r="AG23" s="8">
-        <f t="shared" si="59"/>
-        <v>7.0400124411973088</v>
+        <f t="shared" si="56"/>
+        <v>9.2966822660735282</v>
       </c>
     </row>
     <row r="25" spans="2:139" x14ac:dyDescent="0.3">
@@ -3383,19 +3369,19 @@
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11">
-        <f t="shared" ref="G25:J25" si="60">G3/C3-1</f>
+        <f t="shared" ref="G25:J25" si="57">G3/C3-1</f>
         <v>0.11002645744001471</v>
       </c>
       <c r="H25" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>9.3301435406698774E-2</v>
       </c>
       <c r="I25" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>2.8885946035424492E-2</v>
       </c>
       <c r="J25" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>0.16912581310487074</v>
       </c>
       <c r="K25" s="11">
@@ -3403,28 +3389,28 @@
         <v>0.13627023917152958</v>
       </c>
       <c r="L25" s="11">
-        <f t="shared" ref="L25:N27" si="61">L3/H3-1</f>
-        <v>0.12999999999999989</v>
+        <f t="shared" ref="L25:N27" si="58">L3/H3-1</f>
+        <v>0.32984844801037361</v>
       </c>
       <c r="M25" s="11">
-        <f t="shared" si="61"/>
-        <v>0.12000000000000011</v>
+        <f t="shared" si="58"/>
+        <v>0.26321293540342694</v>
       </c>
       <c r="N25" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="S25" s="11"/>
       <c r="T25" s="11">
-        <f t="shared" ref="T25:V25" si="62">T3/S3-1</f>
+        <f t="shared" ref="T25:V25" si="59">T3/S3-1</f>
         <v>3.1177516040606035E-2</v>
       </c>
       <c r="U25" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>0.38338396821687337</v>
       </c>
       <c r="V25" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>-8.8901089619056739E-3</v>
       </c>
       <c r="W25" s="11">
@@ -3432,8 +3418,8 @@
         <v>0.10099073186321506</v>
       </c>
       <c r="X25" s="11">
-        <f t="shared" ref="X25:X26" si="63">X3/W3-1</f>
-        <v>9.7698113207547177E-2</v>
+        <f t="shared" ref="X25:X26" si="60">X3/W3-1</f>
+        <v>0.17986956942428645</v>
       </c>
     </row>
     <row r="26" spans="2:139" x14ac:dyDescent="0.3">
@@ -3445,48 +3431,48 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11">
-        <f t="shared" ref="G26:K26" si="64">G4/C4-1</f>
+        <f t="shared" ref="G26:K26" si="61">G4/C4-1</f>
         <v>-0.35577942735949097</v>
       </c>
       <c r="H26" s="11">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-0.30128956623681125</v>
       </c>
       <c r="I26" s="11">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-0.26185958254269448</v>
       </c>
       <c r="J26" s="11">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-0.21685878962536032</v>
       </c>
       <c r="K26" s="11">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-1.6460905349794386E-3</v>
       </c>
       <c r="L26" s="11">
-        <f t="shared" si="61"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="58"/>
+        <v>0.11493288590604034</v>
       </c>
       <c r="M26" s="11">
-        <f t="shared" si="61"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="58"/>
+        <v>0.10282776349614386</v>
       </c>
       <c r="N26" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="58"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="S26" s="11"/>
       <c r="T26" s="11">
-        <f t="shared" ref="T26:V26" si="65">T4/S4-1</f>
+        <f t="shared" ref="T26:V26" si="62">T4/S4-1</f>
         <v>0.53672316384180774</v>
       </c>
       <c r="U26" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>6.528186274509804</v>
       </c>
       <c r="V26" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>6.8044929187693448E-2</v>
       </c>
       <c r="W26" s="11">
@@ -3494,8 +3480,8 @@
         <v>-0.28959000152415793</v>
       </c>
       <c r="X26" s="11">
-        <f t="shared" si="63"/>
-        <v>7.1518987341772089E-2</v>
+        <f t="shared" si="60"/>
+        <v>0.10135164127869523</v>
       </c>
     </row>
     <row r="27" spans="2:139" x14ac:dyDescent="0.3">
@@ -3507,48 +3493,48 @@
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11">
-        <f t="shared" ref="G27:K27" si="66">G5/C5-1</f>
+        <f t="shared" ref="G27:K27" si="63">G5/C5-1</f>
         <v>4.1643963571261988E-2</v>
       </c>
       <c r="H27" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>4.1487068965517571E-2</v>
       </c>
       <c r="I27" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>-4.7573739295908579E-3</v>
       </c>
       <c r="J27" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>0.13084178933828805</v>
       </c>
       <c r="K27" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>0.123748318636975</v>
       </c>
       <c r="L27" s="11">
-        <f t="shared" si="61"/>
-        <v>0.12295247949153798</v>
+        <f t="shared" si="58"/>
+        <v>0.31091567511639928</v>
       </c>
       <c r="M27" s="11">
-        <f t="shared" si="61"/>
-        <v>0.11399249889689655</v>
+        <f t="shared" si="58"/>
+        <v>0.2494484483012207</v>
       </c>
       <c r="N27" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="58"/>
         <v>3.2363981042654144E-2</v>
       </c>
       <c r="S27" s="11"/>
       <c r="T27" s="11">
-        <f t="shared" ref="T27:V27" si="67">T5/S5-1</f>
+        <f t="shared" ref="T27:V27" si="64">T5/S5-1</f>
         <v>3.9136622390891773E-2</v>
       </c>
       <c r="U27" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.52644944076694844</v>
       </c>
       <c r="V27" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>-5.6075814501288512E-5</v>
       </c>
       <c r="W27" s="11">
@@ -3557,42 +3543,42 @@
       </c>
       <c r="X27" s="11">
         <f>X5/W5-1</f>
-        <v>9.553216415790966E-2</v>
+        <v>0.17337333143993172</v>
       </c>
       <c r="Y27" s="11">
-        <f t="shared" ref="Y27:AG27" si="68">Y5/X5-1</f>
-        <v>0.7</v>
+        <f t="shared" ref="Y27:AG27" si="65">Y5/X5-1</f>
+        <v>0.40000000000000013</v>
       </c>
       <c r="Z27" s="11">
-        <f t="shared" si="68"/>
-        <v>-6.9999999999999951E-2</v>
+        <f t="shared" si="65"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AA27" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB27" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AC27" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD27" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE27" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF27" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG27" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -3601,35 +3587,35 @@
         <v>46</v>
       </c>
       <c r="C28" s="11">
-        <f t="shared" ref="C28:J28" si="69">C7/C5</f>
+        <f t="shared" ref="C28:J28" si="66">C7/C5</f>
         <v>0.52868373939441105</v>
       </c>
       <c r="D28" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.31973522167487678</v>
       </c>
       <c r="E28" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.49630388640854861</v>
       </c>
       <c r="F28" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.33521509218236384</v>
       </c>
       <c r="G28" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.57622179046480348</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.53794989283866679</v>
       </c>
       <c r="I28" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.55883218120311806</v>
       </c>
       <c r="J28" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.50761453396524481</v>
       </c>
       <c r="K28" s="11">
@@ -3637,31 +3623,31 @@
         <v>0.62840803298310943</v>
       </c>
       <c r="L28" s="11">
-        <f t="shared" ref="L28:N28" si="70">L7/L5</f>
+        <f t="shared" ref="L28:N28" si="67">L7/L5</f>
+        <v>0.55276806855338823</v>
+      </c>
+      <c r="M28" s="11">
+        <f t="shared" si="67"/>
+        <v>0.55650382577987056</v>
+      </c>
+      <c r="N28" s="11">
+        <f t="shared" si="67"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="M28" s="11">
-        <f t="shared" si="70"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="N28" s="11">
-        <f t="shared" si="70"/>
-        <v>0.56999999999999995</v>
-      </c>
       <c r="S28" s="11">
-        <f t="shared" ref="S28:V28" si="71">S7/S5</f>
+        <f t="shared" ref="S28:V28" si="68">S7/S5</f>
         <v>0.54485887096774188</v>
       </c>
       <c r="T28" s="11">
-        <f t="shared" si="71"/>
+        <f t="shared" si="68"/>
         <v>0.56191508787947952</v>
       </c>
       <c r="U28" s="11">
-        <f t="shared" si="71"/>
+        <f t="shared" si="68"/>
         <v>0.4271668629320175</v>
       </c>
       <c r="V28" s="11">
-        <f t="shared" si="71"/>
+        <f t="shared" si="68"/>
         <v>0.41905936892477941</v>
       </c>
       <c r="W28" s="11">
@@ -3670,42 +3656,42 @@
       </c>
       <c r="X28" s="11">
         <f>X7/X5</f>
-        <v>0.58423152764433006</v>
+        <v>0.57519460794309984</v>
       </c>
       <c r="Y28" s="11">
-        <f t="shared" ref="Y28:AG28" si="72">Y7/Y5</f>
+        <f t="shared" ref="Y28:AG28" si="69">Y7/Y5</f>
         <v>0.57999999999999996</v>
       </c>
       <c r="Z28" s="11">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AA28" s="11">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AB28" s="11">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AC28" s="11">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AD28" s="11">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AE28" s="11">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AF28" s="11">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AG28" s="11">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AJ28" s="1" t="s">
@@ -3720,35 +3706,35 @@
         <v>47</v>
       </c>
       <c r="C29" s="11">
-        <f t="shared" ref="C29:J29" si="73">C8/C5</f>
+        <f t="shared" ref="C29:J29" si="70">C8/C5</f>
         <v>0.31088970187592435</v>
       </c>
       <c r="D29" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.25754310344827591</v>
       </c>
       <c r="E29" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.2688282222059577</v>
       </c>
       <c r="F29" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.32070887523224245</v>
       </c>
       <c r="G29" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.32237333731878642</v>
       </c>
       <c r="H29" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.34092084842214171</v>
       </c>
       <c r="I29" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.28599794087365787</v>
       </c>
       <c r="J29" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.25409162717219591</v>
       </c>
       <c r="K29" s="11">
@@ -3756,31 +3742,31 @@
         <v>0.27184466019417475</v>
       </c>
       <c r="L29" s="11">
-        <f t="shared" ref="L29:N29" si="74">L8/L5</f>
-        <v>0.27</v>
+        <f t="shared" ref="L29:N29" si="71">L8/L5</f>
+        <v>0.3025143759161123</v>
       </c>
       <c r="M29" s="11">
-        <f t="shared" si="74"/>
-        <v>0.27</v>
+        <f t="shared" si="71"/>
+        <v>0.25497351383166567</v>
       </c>
       <c r="N29" s="11">
-        <f t="shared" si="74"/>
-        <v>0.27</v>
+        <f t="shared" si="71"/>
+        <v>0.25</v>
       </c>
       <c r="S29" s="11">
-        <f t="shared" ref="S29:V29" si="75">S8/S5</f>
+        <f t="shared" ref="S29:V29" si="72">S8/S5</f>
         <v>0.1319378557874763</v>
       </c>
       <c r="T29" s="11">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.14734078977402421</v>
       </c>
       <c r="U29" s="11">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.2965475990205424</v>
       </c>
       <c r="V29" s="11">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.28977867504112453</v>
       </c>
       <c r="W29" s="11">
@@ -3789,49 +3775,49 @@
       </c>
       <c r="X29" s="11">
         <f>X8/X5</f>
-        <v>0.27044946441794038</v>
+        <v>0.27033942098985891</v>
       </c>
       <c r="Y29" s="11">
-        <f t="shared" ref="Y29:AG29" si="76">Y8/Y5</f>
+        <f t="shared" ref="Y29:AG29" si="73">Y8/Y5</f>
         <v>0</v>
       </c>
       <c r="Z29" s="11">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AA29" s="11">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AB29" s="11">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AC29" s="11">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AD29" s="11">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AE29" s="11">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AF29" s="11">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AG29" s="11">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AJ29" s="1" t="s">
         <v>53</v>
       </c>
       <c r="AK29" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="30" spans="2:139" x14ac:dyDescent="0.3">
@@ -3843,19 +3829,19 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11">
-        <f t="shared" ref="G30:J30" si="77">G9/C9-1</f>
+        <f t="shared" ref="G30:J30" si="74">G9/C9-1</f>
         <v>-7.8792958927074497E-2</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>6.2903920723826001E-2</v>
       </c>
       <c r="I30" s="11">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>3.8362068965517304E-2</v>
       </c>
       <c r="J30" s="11">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>0.21303462321792255</v>
       </c>
       <c r="K30" s="11">
@@ -3863,28 +3849,28 @@
         <v>0.18926296633302986</v>
       </c>
       <c r="L30" s="11">
-        <f t="shared" ref="L30:N30" si="78">L9/H9-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="L30:N30" si="75">L9/H9-1</f>
+        <v>8.6339683826510027E-2</v>
       </c>
       <c r="M30" s="11">
-        <f t="shared" si="78"/>
-        <v>0.12999999999999989</v>
+        <f t="shared" si="75"/>
+        <v>0.1735159817351597</v>
       </c>
       <c r="N30" s="11">
-        <f t="shared" si="78"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="75"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="S30" s="11"/>
       <c r="T30" s="11">
-        <f t="shared" ref="T30:V30" si="79">T9/S9-1</f>
+        <f t="shared" ref="T30:V30" si="76">T9/S9-1</f>
         <v>0.2814371257485031</v>
       </c>
       <c r="U30" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>1.1829808165272997</v>
       </c>
       <c r="V30" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>6.8273997296079303E-2</v>
       </c>
       <c r="W30" s="11">
@@ -3906,7 +3892,7 @@
       </c>
       <c r="AK30" s="6">
         <f>NPV(AK29,X21:EI21)</f>
-        <v>15539.047632985568</v>
+        <v>17170.215017972558</v>
       </c>
     </row>
     <row r="31" spans="2:139" x14ac:dyDescent="0.3">
@@ -3918,19 +3904,19 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11">
-        <f t="shared" ref="G31:J31" si="80">G10/C10-1</f>
+        <f t="shared" ref="G31:J31" si="77">G10/C10-1</f>
         <v>6.3668519454269878E-2</v>
       </c>
       <c r="H31" s="11">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>0.41895681435782373</v>
       </c>
       <c r="I31" s="11">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>0.14909090909090916</v>
       </c>
       <c r="J31" s="11">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>0.31542857142857139</v>
       </c>
       <c r="K31" s="11">
@@ -3938,28 +3924,28 @@
         <v>-1.6627078384798155E-2</v>
       </c>
       <c r="L31" s="11">
-        <f t="shared" ref="L31:N31" si="81">L10/H10-1</f>
-        <v>-5.0000000000000044E-2</v>
+        <f t="shared" ref="L31:N31" si="78">L10/H10-1</f>
+        <v>-0.11067193675889331</v>
       </c>
       <c r="M31" s="11">
-        <f t="shared" si="81"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="78"/>
+        <v>0.15295358649789037</v>
       </c>
       <c r="N31" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="S31" s="11"/>
       <c r="T31" s="11">
-        <f t="shared" ref="T31:V31" si="82">T10/S10-1</f>
+        <f t="shared" ref="T31:V31" si="79">T10/S10-1</f>
         <v>0.31070696721311486</v>
       </c>
       <c r="U31" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="79"/>
         <v>0.64060973226499907</v>
       </c>
       <c r="V31" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="79"/>
         <v>-0.14699225729600951</v>
       </c>
       <c r="W31" s="11">
@@ -3981,7 +3967,7 @@
       </c>
       <c r="AK31" s="6">
         <f>Main!D8</f>
-        <v>-2195.6</v>
+        <v>-631.59999999999991</v>
       </c>
     </row>
     <row r="32" spans="2:139" x14ac:dyDescent="0.3">
@@ -3989,35 +3975,35 @@
         <v>50</v>
       </c>
       <c r="C32" s="11">
-        <f t="shared" ref="C32:J32" si="83">C15/C5</f>
+        <f t="shared" ref="C32:J32" si="80">C15/C5</f>
         <v>-0.15902545341324839</v>
       </c>
       <c r="D32" s="11">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>-0.41848830049261093</v>
       </c>
       <c r="E32" s="11">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>-9.4781526751079648E-2</v>
       </c>
       <c r="F32" s="11">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>-1.938759468343576</v>
       </c>
       <c r="G32" s="11">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>-0.1381706770288447</v>
       </c>
       <c r="H32" s="11">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>-0.21964378094745385</v>
       </c>
       <c r="I32" s="11">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>-9.7146639211648789E-2</v>
       </c>
       <c r="J32" s="11">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>-2.3866666666666672</v>
       </c>
       <c r="K32" s="11">
@@ -4025,31 +4011,31 @@
         <v>1.4363612182471088E-2</v>
       </c>
       <c r="L32" s="11">
-        <f t="shared" ref="L32:N32" si="84">L15/L5</f>
-        <v>-7.7800241795313779E-2</v>
+        <f t="shared" ref="L32:N32" si="81">L15/L5</f>
+        <v>-5.5248618784530128E-2</v>
       </c>
       <c r="M32" s="11">
-        <f t="shared" si="84"/>
-        <v>-4.0379335453295404E-2</v>
+        <f t="shared" si="81"/>
+        <v>-2.2778104767510327E-2</v>
       </c>
       <c r="N32" s="11">
-        <f t="shared" si="84"/>
-        <v>-9.3856704592475054E-2</v>
+        <f t="shared" si="81"/>
+        <v>-6.3518310404011485E-2</v>
       </c>
       <c r="S32" s="11">
-        <f t="shared" ref="S32:V32" si="85">S15/S5</f>
+        <f t="shared" ref="S32:V32" si="82">S15/S5</f>
         <v>0.18661053130929794</v>
       </c>
       <c r="T32" s="11">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>0.13512896598950003</v>
       </c>
       <c r="U32" s="11">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>-0.21779846352268253</v>
       </c>
       <c r="V32" s="11">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>-0.67119036937341092</v>
       </c>
       <c r="W32" s="11">
@@ -4058,50 +4044,50 @@
       </c>
       <c r="X32" s="11">
         <f>X15/X5</f>
-        <v>-5.0409524627377328E-2</v>
+        <v>-3.3110501827749363E-2</v>
       </c>
       <c r="Y32" s="11">
-        <f t="shared" ref="Y32:AG32" si="86">Y15/Y5</f>
-        <v>0.16934990735360103</v>
+        <f t="shared" ref="Y32:AG32" si="83">Y15/Y5</f>
+        <v>0.10204598518004698</v>
       </c>
       <c r="Z32" s="11">
-        <f t="shared" si="86"/>
-        <v>0.16051872256550651</v>
+        <f t="shared" si="83"/>
+        <v>0.18516842254003887</v>
       </c>
       <c r="AA32" s="11">
-        <f t="shared" si="86"/>
-        <v>0.16051872256550653</v>
+        <f t="shared" si="83"/>
+        <v>0.18516842254003887</v>
       </c>
       <c r="AB32" s="11">
-        <f t="shared" si="86"/>
-        <v>0.16051872256550651</v>
+        <f t="shared" si="83"/>
+        <v>0.18516842254003882</v>
       </c>
       <c r="AC32" s="11">
-        <f t="shared" si="86"/>
-        <v>0.16051872256550651</v>
+        <f t="shared" si="83"/>
+        <v>0.18516842254003885</v>
       </c>
       <c r="AD32" s="11">
-        <f t="shared" si="86"/>
-        <v>0.16051872256550642</v>
+        <f t="shared" si="83"/>
+        <v>0.18516842254003879</v>
       </c>
       <c r="AE32" s="11">
-        <f t="shared" si="86"/>
-        <v>0.16051872256550645</v>
+        <f t="shared" si="83"/>
+        <v>0.18516842254003874</v>
       </c>
       <c r="AF32" s="11">
-        <f t="shared" si="86"/>
-        <v>0.16051872256550642</v>
+        <f t="shared" si="83"/>
+        <v>0.18516842254003874</v>
       </c>
       <c r="AG32" s="11">
-        <f t="shared" si="86"/>
-        <v>0.16051872256550642</v>
+        <f t="shared" si="83"/>
+        <v>0.18516842254003876</v>
       </c>
       <c r="AJ32" s="1" t="s">
         <v>56</v>
       </c>
       <c r="AK32" s="6">
         <f>AK30+AK31</f>
-        <v>13343.447632985568</v>
+        <v>16538.615017972559</v>
       </c>
     </row>
     <row r="33" spans="2:37" x14ac:dyDescent="0.3">
@@ -4109,35 +4095,35 @@
         <v>27</v>
       </c>
       <c r="C33" s="11">
-        <f t="shared" ref="C33:J33" si="87">C20/C19</f>
+        <f t="shared" ref="C33:J33" si="84">C20/C19</f>
         <v>0.10004368719965041</v>
       </c>
       <c r="D33" s="11">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>5.7885615251299823E-2</v>
       </c>
       <c r="E33" s="11">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.39855548260013102</v>
       </c>
       <c r="F33" s="11">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>-5.7713327989506673E-2</v>
       </c>
       <c r="G33" s="11">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>-0.23468426013195098</v>
       </c>
       <c r="H33" s="11">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>-0.1270428615479495</v>
       </c>
       <c r="I33" s="11">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.18116415958142573</v>
       </c>
       <c r="J33" s="11">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>1.9911097083037427E-2</v>
       </c>
       <c r="K33" s="11">
@@ -4145,31 +4131,31 @@
         <v>0.13768115942029008</v>
       </c>
       <c r="L33" s="11">
-        <f t="shared" ref="L33:N33" si="88">L20/L19</f>
+        <f t="shared" ref="L33:N33" si="85">L20/L19</f>
+        <v>-0.15930735930735992</v>
+      </c>
+      <c r="M33" s="11">
+        <f t="shared" si="85"/>
+        <v>-0.66487455197132561</v>
+      </c>
+      <c r="N33" s="11">
+        <f t="shared" si="85"/>
         <v>0.1</v>
       </c>
-      <c r="M33" s="11">
-        <f t="shared" si="88"/>
-        <v>0.1</v>
-      </c>
-      <c r="N33" s="11">
-        <f t="shared" si="88"/>
-        <v>0.1</v>
-      </c>
       <c r="S33" s="11">
-        <f t="shared" ref="S33:V33" si="89">S20/S19</f>
+        <f t="shared" ref="S33:V33" si="86">S20/S19</f>
         <v>0.13115963411035703</v>
       </c>
       <c r="T33" s="11">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.10184787279759354</v>
       </c>
       <c r="U33" s="11">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.15947985950227941</v>
       </c>
       <c r="V33" s="11">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>-1.118072809765583E-2</v>
       </c>
       <c r="W33" s="11">
@@ -4178,42 +4164,42 @@
       </c>
       <c r="X33" s="11">
         <f>X20/X19</f>
-        <v>0.10115167313744534</v>
+        <v>-0.12901450905844292</v>
       </c>
       <c r="Y33" s="11">
-        <f t="shared" ref="Y33:AG33" si="90">Y20/Y19</f>
+        <f t="shared" ref="Y33:AG33" si="87">Y20/Y19</f>
         <v>0.15</v>
       </c>
       <c r="Z33" s="11">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
         <v>0.15</v>
       </c>
       <c r="AA33" s="11">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
         <v>0.15</v>
       </c>
       <c r="AB33" s="11">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
         <v>0.15</v>
       </c>
       <c r="AC33" s="11">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
         <v>0.15</v>
       </c>
       <c r="AD33" s="11">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
         <v>0.15</v>
       </c>
       <c r="AE33" s="11">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
         <v>0.15</v>
       </c>
       <c r="AF33" s="11">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
         <v>0.15</v>
       </c>
       <c r="AG33" s="11">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
         <v>0.15</v>
       </c>
       <c r="AJ33" s="1" t="s">
@@ -4221,7 +4207,7 @@
       </c>
       <c r="AK33" s="5">
         <f>AK32/AG22</f>
-        <v>72.322209392875706</v>
+        <v>89.591630649905525</v>
       </c>
     </row>
     <row r="34" spans="2:37" x14ac:dyDescent="0.3">
@@ -4229,35 +4215,35 @@
         <v>51</v>
       </c>
       <c r="C34" s="11">
-        <f t="shared" ref="C34:J34" si="91">C21/C5</f>
+        <f t="shared" ref="C34:J34" si="88">C21/C5</f>
         <v>-0.16034871954541932</v>
       </c>
       <c r="D34" s="11">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-0.41841133004926118</v>
       </c>
       <c r="E34" s="11">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-6.704237722315752E-2</v>
       </c>
       <c r="F34" s="11">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-2.0744604830641706</v>
       </c>
       <c r="G34" s="11">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-0.19578538335076967</v>
       </c>
       <c r="H34" s="11">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-0.2701204641194293</v>
       </c>
       <c r="I34" s="11">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-9.207236358287986E-2</v>
       </c>
       <c r="J34" s="11">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-2.3546287519747242</v>
       </c>
       <c r="K34" s="11">
@@ -4265,31 +4251,31 @@
         <v>-7.9132863412687705E-3</v>
       </c>
       <c r="L34" s="11">
-        <f t="shared" ref="L34:N34" si="92">L21/L5</f>
-        <v>-9.0751171298883118E-2</v>
+        <f t="shared" ref="L34:N34" si="89">L21/L5</f>
+        <v>-7.5487653624985648E-2</v>
       </c>
       <c r="M34" s="11">
-        <f t="shared" si="92"/>
-        <v>-5.7136130213287929E-2</v>
+        <f t="shared" si="89"/>
+        <v>-5.4679223072395554E-2</v>
       </c>
       <c r="N34" s="11">
-        <f t="shared" si="92"/>
-        <v>-0.10375223110993587</v>
+        <f t="shared" si="89"/>
+        <v>-7.1489654260593644E-2</v>
       </c>
       <c r="S34" s="11">
-        <f t="shared" ref="S34:V34" si="93">S21/S5</f>
+        <f t="shared" ref="S34:V34" si="90">S21/S5</f>
         <v>0.17460270398481978</v>
       </c>
       <c r="T34" s="11">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>0.11926500798904352</v>
       </c>
       <c r="U34" s="11">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>-0.21022822856501977</v>
       </c>
       <c r="V34" s="11">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>-0.69990279647076403</v>
       </c>
       <c r="W34" s="11">
@@ -4298,50 +4284,50 @@
       </c>
       <c r="X34" s="11">
         <f>X21/X5</f>
-        <v>-6.575811879535777E-2</v>
+        <v>-5.3778638116544028E-2</v>
       </c>
       <c r="Y34" s="11">
-        <f t="shared" ref="Y34:AG34" si="94">Y21/Y5</f>
-        <v>0.1323456007090324</v>
+        <f t="shared" ref="Y34:AG34" si="91">Y21/Y5</f>
+        <v>7.7745352675164803E-2</v>
       </c>
       <c r="Z34" s="11">
-        <f t="shared" si="94"/>
-        <v>0.12371633681255254</v>
+        <f t="shared" si="91"/>
+        <v>0.14941610748735248</v>
       </c>
       <c r="AA34" s="11">
-        <f t="shared" si="94"/>
-        <v>0.12371633681255254</v>
+        <f t="shared" si="91"/>
+        <v>0.14941610748735251</v>
       </c>
       <c r="AB34" s="11">
-        <f t="shared" si="94"/>
-        <v>0.12359035089801661</v>
+        <f t="shared" si="91"/>
+        <v>0.14933712677773184</v>
       </c>
       <c r="AC34" s="11">
-        <f t="shared" si="94"/>
-        <v>0.12346311759818825</v>
+        <f t="shared" si="91"/>
+        <v>0.1492573640808873</v>
       </c>
       <c r="AD34" s="11">
-        <f t="shared" si="94"/>
-        <v>0.12333462456271796</v>
+        <f t="shared" si="91"/>
+        <v>0.14917681165437094</v>
       </c>
       <c r="AE34" s="11">
-        <f t="shared" si="94"/>
-        <v>0.12320485931897579</v>
+        <f t="shared" si="91"/>
+        <v>0.14909546167907725</v>
       </c>
       <c r="AF34" s="11">
-        <f t="shared" si="94"/>
-        <v>0.12307380927084006</v>
+        <f t="shared" si="91"/>
+        <v>0.14901330625848364</v>
       </c>
       <c r="AG34" s="11">
-        <f t="shared" si="94"/>
-        <v>0.12294146169747534</v>
+        <f t="shared" si="91"/>
+        <v>0.14893033741788414</v>
       </c>
       <c r="AJ34" s="1" t="s">
         <v>58</v>
       </c>
       <c r="AK34" s="5">
         <f>Main!D3</f>
-        <v>249.98</v>
+        <v>223.03</v>
       </c>
     </row>
     <row r="35" spans="2:37" x14ac:dyDescent="0.3">
@@ -4350,7 +4336,7 @@
       </c>
       <c r="AK35" s="12">
         <f>AK33/AK34-1</f>
-        <v>-0.71068801746989474</v>
+        <v>-0.598297849392882</v>
       </c>
     </row>
     <row r="36" spans="2:37" x14ac:dyDescent="0.3">
